--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q10_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0007946783638007924</v>
+        <v>0.0002581212667427773</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007946783638007924</v>
+        <v>0.0002581212667427773</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0007905670663422326</v>
+        <v>0.0002565107376172436</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007905670663422326</v>
+        <v>0.0002565107376172436</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0007839279075778974</v>
+        <v>0.0002539689045719737</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007839279075778974</v>
+        <v>0.0002539689045719737</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0007755402490116014</v>
+        <v>0.0002508890017103967</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007755402490116014</v>
+        <v>0.0002508890017103967</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0007676472214052138</v>
+        <v>0.0002479817984761484</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0007676472214052138</v>
+        <v>0.0002479817984761484</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.000762404792587385</v>
+        <v>0.0002461566809990899</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000762404792587385</v>
+        <v>0.0002461566809990899</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0007616290142824216</v>
+        <v>0.0002459964334765912</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007616290142824216</v>
+        <v>0.0002459964334765912</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0007675198157825046</v>
+        <v>0.0002481969457911115</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0007675198157825046</v>
+        <v>0.0002481969457911115</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0007835133428220556</v>
+        <v>0.0002539003219989963</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0007835133428220556</v>
+        <v>0.0002539003219989963</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0008094471694951859</v>
+        <v>0.0002630334418241405</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0008094471694951859</v>
+        <v>0.0002630334418241405</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0008480840975810085</v>
+        <v>0.0002764797488273825</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0008480840975810085</v>
+        <v>0.0002764797488273825</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0009012734548318484</v>
+        <v>0.0002948371625523488</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0009012734548318484</v>
+        <v>0.0002948371625523488</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0009702775873375611</v>
+        <v>0.0003184913130965887</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0009702775873375611</v>
+        <v>0.0003184913130965887</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001055534809683504</v>
+        <v>0.0003475548568192467</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001055534809683504</v>
+        <v>0.0003475548568192467</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001156542173821867</v>
+        <v>0.0003819601265026586</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001156542173821867</v>
+        <v>0.0003819601265026586</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.001272055647520686</v>
+        <v>0.0004208527269778005</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001272055647520686</v>
+        <v>0.0004208527269778005</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.001398806503115964</v>
+        <v>0.0004634643198599986</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001398806503115964</v>
+        <v>0.0004634643198599986</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.001534270399026923</v>
+        <v>0.0005087631320300311</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001534270399026923</v>
+        <v>0.0005087631320300311</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.001676961996232491</v>
+        <v>0.0005562130458147062</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001676961996232491</v>
+        <v>0.0005562130458147062</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.00182111181773815</v>
+        <v>0.000603798401735998</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00182111181773815</v>
+        <v>0.000603798401735998</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.001967949055021488</v>
+        <v>0.0006519875671467485</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001967949055021488</v>
+        <v>0.0006519875671467485</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.002114396747654023</v>
+        <v>0.0006997714573873175</v>
       </c>
       <c r="C23" t="n">
-        <v>0.002114396747654023</v>
+        <v>0.0006997714573873175</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.002258383089407051</v>
+        <v>0.0007465326646766203</v>
       </c>
       <c r="C24" t="n">
-        <v>0.002258383089407051</v>
+        <v>0.0007465326646766203</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.002404701164377656</v>
+        <v>0.0007939709097449857</v>
       </c>
       <c r="C25" t="n">
-        <v>0.002404701164377656</v>
+        <v>0.0007939709097449857</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.002560783152935461</v>
+        <v>0.0008446775202898941</v>
       </c>
       <c r="C26" t="n">
-        <v>0.002560783152935461</v>
+        <v>0.0008446775202898941</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.002727072976844506</v>
+        <v>0.0008988944312041769</v>
       </c>
       <c r="C27" t="n">
-        <v>0.002727072976844506</v>
+        <v>0.0008988944312041769</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.00290329828187595</v>
+        <v>0.0009565962214813715</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00290329828187595</v>
+        <v>0.0009565962214813715</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.00308842370023175</v>
+        <v>0.001017475242548905</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00308842370023175</v>
+        <v>0.001017475242548905</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.00328667047841536</v>
+        <v>0.001082918482655423</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00328667047841536</v>
+        <v>0.001082918482655423</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.003484472145298599</v>
+        <v>0.001148471654417221</v>
       </c>
       <c r="C31" t="n">
-        <v>0.003484472145298599</v>
+        <v>0.001148471654417221</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
